--- a/results/reports/year_2024_report.xlsx
+++ b/results/reports/year_2024_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,21 +582,27 @@
         <v>39.43</v>
       </c>
       <c r="M2" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="O2" t="n">
         <v>32.66</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>36.56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>3.63</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>-2.43</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>-4.43</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>9.06</v>
       </c>
     </row>
@@ -647,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978425524804582</v>
+        <v>0.6978425524804581</v>
       </c>
       <c r="E2" t="n">
         <v>0.3715</v>
@@ -687,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6644616479194478</v>
+        <v>0.6644616479194476</v>
       </c>
       <c r="E4" t="n">
         <v>13.5807</v>
@@ -707,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.655603960827012</v>
+        <v>0.6556039608270122</v>
       </c>
       <c r="E5" t="n">
         <v>0.8264</v>
@@ -787,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6454966613487517</v>
+        <v>0.6454966613487518</v>
       </c>
       <c r="E9" t="n">
         <v>1.4303</v>
@@ -807,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.638684088198757</v>
+        <v>0.6386840881987571</v>
       </c>
       <c r="E10" t="n">
         <v>1.8858</v>
@@ -827,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6333889836431563</v>
+        <v>0.6333889836431564</v>
       </c>
       <c r="E11" t="n">
         <v>9.722200000000001</v>
@@ -987,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6231556928364372</v>
+        <v>0.6231556928364373</v>
       </c>
       <c r="E19" t="n">
         <v>0.6764</v>
@@ -1027,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6216706334092146</v>
+        <v>0.6216706334092145</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5668</v>
@@ -1193,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6405392352124768</v>
+        <v>0.6405392352124767</v>
       </c>
       <c r="E7" t="n">
         <v>8.7516</v>
@@ -1213,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.634991227013089</v>
+        <v>0.6349912270130889</v>
       </c>
       <c r="E8" t="n">
         <v>7.7569</v>
@@ -1293,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6300787244033424</v>
+        <v>0.6300787244033426</v>
       </c>
       <c r="E12" t="n">
         <v>4.4733</v>
@@ -1579,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6756533694046596</v>
+        <v>0.6756533694046594</v>
       </c>
       <c r="E4" t="n">
         <v>-3.7037</v>
@@ -1699,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6554928953192253</v>
+        <v>0.6554928953192254</v>
       </c>
       <c r="E10" t="n">
         <v>0.6605</v>
@@ -1719,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6548487180627626</v>
+        <v>0.6548487180627628</v>
       </c>
       <c r="E11" t="n">
         <v>-2.4745</v>
@@ -1819,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6477409153575396</v>
+        <v>0.6477409153575395</v>
       </c>
       <c r="E16" t="n">
         <v>-0.8211000000000001</v>
@@ -1859,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6465154471219584</v>
+        <v>0.6465154471219585</v>
       </c>
       <c r="E18" t="n">
         <v>0.801</v>
@@ -1879,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6462534648277731</v>
+        <v>0.646253464827773</v>
       </c>
       <c r="E19" t="n">
         <v>2.9672</v>
@@ -2165,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6499372214748779</v>
+        <v>0.649937221474878</v>
       </c>
       <c r="E11" t="n">
         <v>1.1522</v>
@@ -2185,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6452310167465193</v>
+        <v>0.6452310167465194</v>
       </c>
       <c r="E12" t="n">
         <v>19.9239</v>
@@ -2325,7 +2341,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6288495626342244</v>
+        <v>0.6288495626342243</v>
       </c>
       <c r="E19" t="n">
         <v>-3.168</v>
@@ -2365,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6276889311369293</v>
+        <v>0.6276889311369294</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9346</v>
@@ -2431,7 +2447,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978824958340608</v>
+        <v>0.6978824958340607</v>
       </c>
       <c r="E2" t="n">
         <v>-2.1488</v>
@@ -2491,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6835628436471304</v>
+        <v>0.6835628436471302</v>
       </c>
       <c r="E5" t="n">
         <v>0.5996</v>
@@ -2511,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6776627700020331</v>
+        <v>0.677662770002033</v>
       </c>
       <c r="E6" t="n">
         <v>10.8214</v>
@@ -2531,7 +2547,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6773319558547038</v>
+        <v>0.6773319558547037</v>
       </c>
       <c r="E7" t="n">
         <v>1.2933</v>
@@ -2551,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6768227693357187</v>
+        <v>0.6768227693357186</v>
       </c>
       <c r="E8" t="n">
         <v>2.8551</v>
@@ -2571,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6756763055263952</v>
+        <v>0.6756763055263955</v>
       </c>
       <c r="E9" t="n">
         <v>2.6953</v>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6748667723620294</v>
+        <v>0.6748667723620295</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1575</v>
@@ -2651,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6673911572826161</v>
+        <v>0.667391157282616</v>
       </c>
       <c r="E13" t="n">
         <v>22.2078</v>
@@ -2671,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6663495588692312</v>
+        <v>0.6663495588692315</v>
       </c>
       <c r="E14" t="n">
         <v>-2.1324</v>
@@ -2691,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6635289018462968</v>
+        <v>0.6635289018462965</v>
       </c>
       <c r="E15" t="n">
         <v>0.0626</v>
@@ -2711,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6619570252890482</v>
+        <v>0.661957025289048</v>
       </c>
       <c r="E16" t="n">
         <v>2.8026</v>
@@ -2897,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7274771975114342</v>
+        <v>0.727477197511434</v>
       </c>
       <c r="E3" t="n">
         <v>2.8002</v>
@@ -2917,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6926411430159818</v>
+        <v>0.692641143015982</v>
       </c>
       <c r="E4" t="n">
         <v>8.4793</v>
@@ -2937,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6906641060153409</v>
+        <v>0.690664106015341</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1364</v>
@@ -3037,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6698461574753177</v>
+        <v>0.6698461574753176</v>
       </c>
       <c r="E10" t="n">
         <v>6.6743</v>
@@ -3097,7 +3113,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6641250449684154</v>
+        <v>0.6641250449684152</v>
       </c>
       <c r="E13" t="n">
         <v>11.2059</v>
@@ -3237,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6439159046561547</v>
+        <v>0.6439159046561548</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6855</v>
@@ -3257,7 +3273,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6430933728526371</v>
+        <v>0.6430933728526369</v>
       </c>
       <c r="E21" t="n">
         <v>10.0635</v>
@@ -3277,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,25 +3314,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3333,18 +3354,21 @@
         <v>4.25</v>
       </c>
       <c r="D2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E2" t="n">
         <v>1.97</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-1.65</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1.94</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.73</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-2.17</v>
       </c>
     </row>
@@ -3359,18 +3383,21 @@
         <v>2.65</v>
       </c>
       <c r="D3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E3" t="n">
         <v>4.34</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4.08</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2.18</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-2.76</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>-0.96</v>
       </c>
     </row>
@@ -3385,18 +3412,21 @@
         <v>-0.18</v>
       </c>
       <c r="D4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2.67</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2.44</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-0.77</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -3411,18 +3441,21 @@
         <v>2.46</v>
       </c>
       <c r="D5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E5" t="n">
         <v>3.78</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.51</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-1.97</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.52</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3.24</v>
       </c>
     </row>
@@ -3437,18 +3470,21 @@
         <v>0.04</v>
       </c>
       <c r="D6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E6" t="n">
         <v>-0.08</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.87</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>4.05</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3.84</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5.06</v>
       </c>
     </row>
@@ -3463,18 +3499,21 @@
         <v>3.19</v>
       </c>
       <c r="D7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E7" t="n">
         <v>2.29</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-1.33</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-1.45</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-2.93</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-1.26</v>
       </c>
     </row>
@@ -3489,18 +3528,21 @@
         <v>2.96</v>
       </c>
       <c r="D8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E8" t="n">
         <v>1.08</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2.93</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.03</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -3515,18 +3557,21 @@
         <v>3.08</v>
       </c>
       <c r="D9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E9" t="n">
         <v>2.27</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-0.51</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-1.06</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>3.14</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-1.36</v>
       </c>
     </row>
@@ -3541,18 +3586,21 @@
         <v>2.6</v>
       </c>
       <c r="D10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E10" t="n">
         <v>2.29</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.17</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-1.98</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-1.61</v>
       </c>
     </row>
@@ -3567,18 +3615,21 @@
         <v>1.9</v>
       </c>
       <c r="D11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-5.54</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1.07</v>
       </c>
     </row>
@@ -3593,18 +3644,21 @@
         <v>2.06</v>
       </c>
       <c r="D12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E12" t="n">
         <v>2.33</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-1.12</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-1.26</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-3.1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1.59</v>
       </c>
     </row>
@@ -3619,18 +3673,21 @@
         <v>5.94</v>
       </c>
       <c r="D13" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="E13" t="n">
         <v>7.15</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-1.22</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-4.06</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-0.43</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-2.01</v>
       </c>
     </row>
@@ -3937,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7106693481078596</v>
+        <v>0.7106693481078595</v>
       </c>
       <c r="E3" t="n">
         <v>3.057</v>
@@ -3957,7 +4014,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6779855098628234</v>
+        <v>0.6779855098628232</v>
       </c>
       <c r="E4" t="n">
         <v>0.9258999999999999</v>
@@ -3977,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6724670800507139</v>
+        <v>0.672467080050714</v>
       </c>
       <c r="E5" t="n">
         <v>-1.0617</v>
@@ -4117,7 +4174,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6480818695992224</v>
+        <v>0.6480818695992225</v>
       </c>
       <c r="E12" t="n">
         <v>11.9195</v>
@@ -4137,7 +4194,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6478870863647489</v>
+        <v>0.6478870863647488</v>
       </c>
       <c r="E13" t="n">
         <v>0.5041</v>
@@ -4157,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6456158620708566</v>
+        <v>0.6456158620708569</v>
       </c>
       <c r="E14" t="n">
         <v>44.4095</v>
@@ -4197,7 +4254,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6398821150419485</v>
+        <v>0.6398821150419486</v>
       </c>
       <c r="E16" t="n">
         <v>2.2864</v>
@@ -4217,7 +4274,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6370473214656563</v>
+        <v>0.6370473214656565</v>
       </c>
       <c r="E17" t="n">
         <v>7.7662</v>
@@ -4277,7 +4334,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6288590031313812</v>
+        <v>0.6288590031313813</v>
       </c>
       <c r="E20" t="n">
         <v>6.5789</v>
@@ -4363,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7555104604490829</v>
+        <v>0.7555104604490828</v>
       </c>
       <c r="E2" t="n">
         <v>31.9843</v>
@@ -4403,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6726468382878256</v>
+        <v>0.6726468382878253</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1311</v>
@@ -4583,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6456307333613616</v>
+        <v>0.6456307333613617</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8479</v>
@@ -4623,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6394514174100402</v>
+        <v>0.6394514174100401</v>
       </c>
       <c r="E15" t="n">
         <v>-6.6547</v>
@@ -4663,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6331409183104717</v>
+        <v>0.6331409183104716</v>
       </c>
       <c r="E17" t="n">
         <v>6.8302</v>
@@ -4829,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6732030541732315</v>
+        <v>0.6732030541732316</v>
       </c>
       <c r="E3" t="n">
         <v>0.9026</v>
@@ -4969,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.642862141998631</v>
+        <v>0.6428621419986308</v>
       </c>
       <c r="E10" t="n">
         <v>0.6418</v>
@@ -5069,7 +5126,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6362436471346519</v>
+        <v>0.6362436471346516</v>
       </c>
       <c r="E15" t="n">
         <v>-10.1493</v>
@@ -5109,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6330971385323407</v>
+        <v>0.6330971385323408</v>
       </c>
       <c r="E17" t="n">
         <v>9.148099999999999</v>
@@ -5149,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6246746430724661</v>
+        <v>0.6246746430724659</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4505</v>
@@ -5169,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6242786318911265</v>
+        <v>0.6242786318911263</v>
       </c>
       <c r="E20" t="n">
         <v>1.2022</v>
@@ -5189,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6196458505525597</v>
+        <v>0.6196458505525596</v>
       </c>
       <c r="E21" t="n">
         <v>-5.9091</v>
@@ -5295,7 +5352,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6523070681550629</v>
+        <v>0.6523070681550631</v>
       </c>
       <c r="E4" t="n">
         <v>3.8711</v>
@@ -5315,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6497625116481487</v>
+        <v>0.6497625116481488</v>
       </c>
       <c r="E5" t="n">
         <v>-0.8649</v>
@@ -5335,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6496717330284841</v>
+        <v>0.6496717330284842</v>
       </c>
       <c r="E6" t="n">
         <v>2.6538</v>
@@ -5355,7 +5412,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6484448327097736</v>
+        <v>0.6484448327097735</v>
       </c>
       <c r="E7" t="n">
         <v>4.4589</v>
@@ -5615,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6303257808403836</v>
+        <v>0.6303257808403838</v>
       </c>
       <c r="E20" t="n">
         <v>3.1819</v>
@@ -5721,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6784074096967706</v>
+        <v>0.6784074096967707</v>
       </c>
       <c r="E3" t="n">
         <v>-9.2309</v>
@@ -5841,7 +5898,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6378877143667725</v>
+        <v>0.6378877143667726</v>
       </c>
       <c r="E9" t="n">
         <v>-1.169</v>
@@ -5861,7 +5918,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6375393073270097</v>
+        <v>0.6375393073270098</v>
       </c>
       <c r="E10" t="n">
         <v>0.3968</v>
@@ -5881,7 +5938,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6351398837663508</v>
+        <v>0.6351398837663507</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8038</v>
@@ -5921,7 +5978,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6318557193833665</v>
+        <v>0.6318557193833664</v>
       </c>
       <c r="E13" t="n">
         <v>-2.1886</v>
@@ -5981,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6239144071664557</v>
+        <v>0.6239144071664556</v>
       </c>
       <c r="E16" t="n">
         <v>3.4401</v>
@@ -6001,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6230519539983551</v>
+        <v>0.623051953998355</v>
       </c>
       <c r="E17" t="n">
         <v>5.2152</v>
@@ -6021,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6228141128826767</v>
+        <v>0.6228141128826766</v>
       </c>
       <c r="E18" t="n">
         <v>-3.2264</v>
@@ -6041,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6222082175082194</v>
+        <v>0.6222082175082193</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2684</v>
@@ -6147,7 +6204,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6856473379269339</v>
+        <v>0.6856473379269338</v>
       </c>
       <c r="E2" t="n">
         <v>2.1575</v>
@@ -6167,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6638481763577682</v>
+        <v>0.6638481763577683</v>
       </c>
       <c r="E3" t="n">
         <v>1.1194</v>
@@ -6447,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6337538117262445</v>
+        <v>0.6337538117262443</v>
       </c>
       <c r="E17" t="n">
         <v>5.7026</v>
@@ -6487,7 +6544,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6320243646771911</v>
+        <v>0.6320243646771909</v>
       </c>
       <c r="E19" t="n">
         <v>0.6793</v>

--- a/results/reports/year_2024_report.xlsx
+++ b/results/reports/year_2024_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978425524804581</v>
+        <v>0.6978425524804582</v>
       </c>
       <c r="E2" t="n">
         <v>0.3715</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6644616479194476</v>
+        <v>0.6644616479194478</v>
       </c>
       <c r="E4" t="n">
         <v>13.5807</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6386840881987571</v>
+        <v>0.638684088198757</v>
       </c>
       <c r="E10" t="n">
         <v>1.8858</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6333889836431564</v>
+        <v>0.6333889836431563</v>
       </c>
       <c r="E11" t="n">
         <v>9.722200000000001</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6301691899416976</v>
+        <v>0.6301691899416975</v>
       </c>
       <c r="E13" t="n">
         <v>0.4109</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.629117545306901</v>
+        <v>0.6291175453069011</v>
       </c>
       <c r="E14" t="n">
         <v>-1.2925</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6231556928364373</v>
+        <v>0.6231556928364372</v>
       </c>
       <c r="E19" t="n">
         <v>0.6764</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6662507593345611</v>
+        <v>0.666250759334561</v>
       </c>
       <c r="E4" t="n">
         <v>0.5495</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6520104700869785</v>
+        <v>0.6520104700869784</v>
       </c>
       <c r="E5" t="n">
         <v>9.591799999999999</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6405392352124767</v>
+        <v>0.6405392352124768</v>
       </c>
       <c r="E7" t="n">
         <v>8.7516</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6193358052792194</v>
+        <v>0.6193358052792195</v>
       </c>
       <c r="E17" t="n">
         <v>2.1436</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6756533694046594</v>
+        <v>0.6756533694046596</v>
       </c>
       <c r="E4" t="n">
         <v>-3.7037</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6661991219847834</v>
+        <v>0.6661991219847831</v>
       </c>
       <c r="E6" t="n">
         <v>7.3221</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6603843315859463</v>
+        <v>0.6603843315859464</v>
       </c>
       <c r="E7" t="n">
         <v>8.3833</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6588613190753914</v>
+        <v>0.6588613190753915</v>
       </c>
       <c r="E8" t="n">
         <v>25.2874</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6554928953192254</v>
+        <v>0.6554928953192253</v>
       </c>
       <c r="E10" t="n">
         <v>0.6605</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6548487180627628</v>
+        <v>0.6548487180627626</v>
       </c>
       <c r="E11" t="n">
         <v>-2.4745</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6503970502572092</v>
+        <v>0.6503970502572091</v>
       </c>
       <c r="E13" t="n">
         <v>2.2599</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6502124792741607</v>
+        <v>0.6502124792741606</v>
       </c>
       <c r="E14" t="n">
         <v>0.3047</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6477409153575395</v>
+        <v>0.6477409153575396</v>
       </c>
       <c r="E16" t="n">
         <v>-0.8211000000000001</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6475520354298492</v>
+        <v>0.647552035429849</v>
       </c>
       <c r="E17" t="n">
         <v>-9.761900000000001</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6465154471219585</v>
+        <v>0.6465154471219583</v>
       </c>
       <c r="E18" t="n">
         <v>0.801</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6374165051663888</v>
+        <v>0.6374165051663887</v>
       </c>
       <c r="E20" t="n">
         <v>-2.3281</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.660872812775902</v>
+        <v>0.6608728127759023</v>
       </c>
       <c r="E9" t="n">
         <v>4.2716</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.649937221474878</v>
+        <v>0.6499372214748779</v>
       </c>
       <c r="E11" t="n">
         <v>1.1522</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6418525746447509</v>
+        <v>0.6418525746447508</v>
       </c>
       <c r="E13" t="n">
         <v>-1.0482</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6288495626342243</v>
+        <v>0.6288495626342244</v>
       </c>
       <c r="E19" t="n">
         <v>-3.168</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6974513932430905</v>
+        <v>0.6974513932430907</v>
       </c>
       <c r="E3" t="n">
         <v>2.2262</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6835628436471302</v>
+        <v>0.6835628436471304</v>
       </c>
       <c r="E5" t="n">
         <v>0.5996</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.677662770002033</v>
+        <v>0.6776627700020331</v>
       </c>
       <c r="E6" t="n">
         <v>10.8214</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6773319558547037</v>
+        <v>0.6773319558547038</v>
       </c>
       <c r="E7" t="n">
         <v>1.2933</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6768227693357186</v>
+        <v>0.6768227693357187</v>
       </c>
       <c r="E8" t="n">
         <v>2.8551</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6756763055263955</v>
+        <v>0.6756763055263952</v>
       </c>
       <c r="E9" t="n">
         <v>2.6953</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6663495588692315</v>
+        <v>0.6663495588692314</v>
       </c>
       <c r="E14" t="n">
         <v>-2.1324</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.661957025289048</v>
+        <v>0.6619570252890483</v>
       </c>
       <c r="E16" t="n">
         <v>2.8026</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6596991165962786</v>
+        <v>0.6596991165962787</v>
       </c>
       <c r="E17" t="n">
         <v>-2.4105</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6596266817461549</v>
+        <v>0.659626681746155</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2644</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.690664106015341</v>
+        <v>0.6906641060153409</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1364</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6698461574753176</v>
+        <v>0.6698461574753177</v>
       </c>
       <c r="E10" t="n">
         <v>6.6743</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6641250449684152</v>
+        <v>0.6641250449684155</v>
       </c>
       <c r="E13" t="n">
         <v>11.2059</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6537748658651391</v>
+        <v>0.6537748658651392</v>
       </c>
       <c r="E17" t="n">
         <v>-0.9923</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6470016930762671</v>
+        <v>0.6470016930762672</v>
       </c>
       <c r="E18" t="n">
         <v>6.9308</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7206311037398363</v>
+        <v>0.7206311037398362</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7252</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7106693481078595</v>
+        <v>0.7106693481078596</v>
       </c>
       <c r="E3" t="n">
         <v>3.057</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.672467080050714</v>
+        <v>0.6724670800507139</v>
       </c>
       <c r="E5" t="n">
         <v>-1.0617</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6456158620708569</v>
+        <v>0.6456158620708566</v>
       </c>
       <c r="E14" t="n">
         <v>44.4095</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6400164134402633</v>
+        <v>0.6400164134402634</v>
       </c>
       <c r="E15" t="n">
         <v>2.0361</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6398821150419486</v>
+        <v>0.6398821150419485</v>
       </c>
       <c r="E16" t="n">
         <v>2.2864</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6293237475647263</v>
+        <v>0.6293237475647262</v>
       </c>
       <c r="E19" t="n">
         <v>16.1728</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7555104604490828</v>
+        <v>0.7555104604490829</v>
       </c>
       <c r="E2" t="n">
         <v>31.9843</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6726468382878253</v>
+        <v>0.6726468382878256</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1311</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6663811499404041</v>
+        <v>0.666381149940404</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1418</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6456307333613617</v>
+        <v>0.6456307333613616</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8479</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6394514174100401</v>
+        <v>0.63945141741004</v>
       </c>
       <c r="E15" t="n">
         <v>-6.6547</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6279286500837663</v>
+        <v>0.6279286500837664</v>
       </c>
       <c r="E19" t="n">
         <v>-7.764</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6668209222370837</v>
+        <v>0.6668209222370836</v>
       </c>
       <c r="E4" t="n">
         <v>-2.5341</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6457214997488587</v>
+        <v>0.6457214997488588</v>
       </c>
       <c r="E7" t="n">
         <v>-1.6947</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.643795846025967</v>
+        <v>0.6437958460259671</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8333</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6432209526069954</v>
+        <v>0.6432209526069953</v>
       </c>
       <c r="E9" t="n">
         <v>5.0911</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6381690166530872</v>
+        <v>0.6381690166530873</v>
       </c>
       <c r="E13" t="n">
         <v>10.571</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6362436471346516</v>
+        <v>0.6362436471346519</v>
       </c>
       <c r="E15" t="n">
         <v>-10.1493</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6360770549312598</v>
+        <v>0.6360770549312599</v>
       </c>
       <c r="E16" t="n">
         <v>0.625</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6319940867141862</v>
+        <v>0.6319940867141863</v>
       </c>
       <c r="E18" t="n">
         <v>-13.9333</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6246746430724659</v>
+        <v>0.624674643072466</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4505</v>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6523070681550631</v>
+        <v>0.6523070681550629</v>
       </c>
       <c r="E4" t="n">
         <v>3.8711</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6469194589572085</v>
+        <v>0.6469194589572084</v>
       </c>
       <c r="E10" t="n">
         <v>4.6038</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6378877143667726</v>
+        <v>0.6378877143667725</v>
       </c>
       <c r="E9" t="n">
         <v>-1.169</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6351398837663507</v>
+        <v>0.6351398837663508</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8038</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6318557193833664</v>
+        <v>0.6318557193833665</v>
       </c>
       <c r="E13" t="n">
         <v>-2.1886</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.627034930996516</v>
+        <v>0.6270349309965159</v>
       </c>
       <c r="E15" t="n">
         <v>1.7999</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6239144071664556</v>
+        <v>0.6239144071664555</v>
       </c>
       <c r="E16" t="n">
         <v>3.4401</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.623051953998355</v>
+        <v>0.6230519539983551</v>
       </c>
       <c r="E17" t="n">
         <v>5.2152</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6228141128826766</v>
+        <v>0.6228141128826765</v>
       </c>
       <c r="E18" t="n">
         <v>-3.2264</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6638481763577683</v>
+        <v>0.6638481763577682</v>
       </c>
       <c r="E3" t="n">
         <v>1.1194</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6422698529543591</v>
+        <v>0.6422698529543589</v>
       </c>
       <c r="E13" t="n">
         <v>8.254899999999999</v>

--- a/results/reports/year_2024_report.xlsx
+++ b/results/reports/year_2024_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978425524804582</v>
+        <v>0.6978425524804581</v>
       </c>
       <c r="E2" t="n">
         <v>0.3715</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.648019665059724</v>
+        <v>0.6480196650597242</v>
       </c>
       <c r="E8" t="n">
         <v>5.265</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.638684088198757</v>
+        <v>0.6386840881987571</v>
       </c>
       <c r="E10" t="n">
         <v>1.8858</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6326251591787279</v>
+        <v>0.632625159178728</v>
       </c>
       <c r="E12" t="n">
         <v>-3.4037</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6291175453069011</v>
+        <v>0.6291175453069012</v>
       </c>
       <c r="E14" t="n">
         <v>-1.2925</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6263379394677504</v>
+        <v>0.6263379394677503</v>
       </c>
       <c r="E15" t="n">
         <v>7.5023</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6243024707943736</v>
+        <v>0.6243024707943738</v>
       </c>
       <c r="E17" t="n">
         <v>2.6484</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6216706334092145</v>
+        <v>0.6216706334092146</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5668</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6942679918661071</v>
+        <v>0.6942679918661072</v>
       </c>
       <c r="E2" t="n">
         <v>6.7517</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6694470348391423</v>
+        <v>0.6694470348391421</v>
       </c>
       <c r="E3" t="n">
         <v>-2.7625</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.666250759334561</v>
+        <v>0.6662507593345611</v>
       </c>
       <c r="E4" t="n">
         <v>0.5495</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6405392352124768</v>
+        <v>0.6405392352124767</v>
       </c>
       <c r="E7" t="n">
         <v>8.7516</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6300787244033426</v>
+        <v>0.6300787244033423</v>
       </c>
       <c r="E12" t="n">
         <v>4.4733</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6193358052792195</v>
+        <v>0.6193358052792194</v>
       </c>
       <c r="E17" t="n">
         <v>2.1436</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6133464344468578</v>
+        <v>0.6133464344468577</v>
       </c>
       <c r="E20" t="n">
         <v>3.2636</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6083093973797046</v>
+        <v>0.6083093973797047</v>
       </c>
       <c r="E21" t="n">
         <v>3.8251</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6899846102587927</v>
+        <v>0.6899846102587928</v>
       </c>
       <c r="E2" t="n">
         <v>-2.4228</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6756533694046596</v>
+        <v>0.6756533694046594</v>
       </c>
       <c r="E4" t="n">
         <v>-3.7037</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6603843315859464</v>
+        <v>0.6603843315859463</v>
       </c>
       <c r="E7" t="n">
         <v>8.3833</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6554928953192253</v>
+        <v>0.6554928953192254</v>
       </c>
       <c r="E10" t="n">
         <v>0.6605</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6548487180627626</v>
+        <v>0.6548487180627628</v>
       </c>
       <c r="E11" t="n">
         <v>-2.4745</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6502124792741606</v>
+        <v>0.6502124792741607</v>
       </c>
       <c r="E14" t="n">
         <v>0.3047</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6477409153575396</v>
+        <v>0.6477409153575399</v>
       </c>
       <c r="E16" t="n">
         <v>-0.8211000000000001</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6465154471219583</v>
+        <v>0.6465154471219584</v>
       </c>
       <c r="E18" t="n">
         <v>0.801</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6374165051663887</v>
+        <v>0.6374165051663888</v>
       </c>
       <c r="E20" t="n">
         <v>-2.3281</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6736999274289488</v>
+        <v>0.6736999274289489</v>
       </c>
       <c r="E4" t="n">
         <v>1.025</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6727657373198934</v>
+        <v>0.6727657373198936</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2786</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.670035567466495</v>
+        <v>0.6700355674664951</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6652</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6452310167465194</v>
+        <v>0.6452310167465193</v>
       </c>
       <c r="E12" t="n">
         <v>19.9239</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978824958340607</v>
+        <v>0.6978824958340608</v>
       </c>
       <c r="E2" t="n">
         <v>-2.1488</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6974513932430907</v>
+        <v>0.6974513932430905</v>
       </c>
       <c r="E3" t="n">
         <v>2.2262</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6756763055263952</v>
+        <v>0.6756763055263955</v>
       </c>
       <c r="E9" t="n">
         <v>2.6953</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6748667723620295</v>
+        <v>0.6748667723620294</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1575</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6663495588692314</v>
+        <v>0.6663495588692312</v>
       </c>
       <c r="E14" t="n">
         <v>-2.1324</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6596991165962787</v>
+        <v>0.6596991165962786</v>
       </c>
       <c r="E17" t="n">
         <v>-2.4105</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.659626681746155</v>
+        <v>0.6596266817461549</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2644</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.727477197511434</v>
+        <v>0.7274771975114342</v>
       </c>
       <c r="E3" t="n">
         <v>2.8002</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.692641143015982</v>
+        <v>0.6926411430159818</v>
       </c>
       <c r="E4" t="n">
         <v>8.4793</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6906641060153409</v>
+        <v>0.690664106015341</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1364</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6864711013497827</v>
+        <v>0.6864711013497826</v>
       </c>
       <c r="E6" t="n">
         <v>12.4972</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6684340203428591</v>
+        <v>0.6684340203428593</v>
       </c>
       <c r="E12" t="n">
         <v>4.2262</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6567025849273826</v>
+        <v>0.6567025849273825</v>
       </c>
       <c r="E16" t="n">
         <v>0.4222</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6439159046561548</v>
+        <v>0.6439159046561547</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6855</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7206311037398362</v>
+        <v>0.7206311037398363</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7252</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7106693481078596</v>
+        <v>0.7106693481078595</v>
       </c>
       <c r="E3" t="n">
         <v>3.057</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6545568736746454</v>
+        <v>0.6545568736746457</v>
       </c>
       <c r="E11" t="n">
         <v>-1.5427</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6400164134402634</v>
+        <v>0.6400164134402633</v>
       </c>
       <c r="E15" t="n">
         <v>2.0361</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6293237475647262</v>
+        <v>0.6293237475647263</v>
       </c>
       <c r="E19" t="n">
         <v>16.1728</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6635045250941431</v>
+        <v>0.6635045250941433</v>
       </c>
       <c r="E7" t="n">
         <v>14.7174</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6585963994769185</v>
+        <v>0.6585963994769186</v>
       </c>
       <c r="E8" t="n">
         <v>6.4058</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6456307333613616</v>
+        <v>0.6456307333613617</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8479</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.63945141741004</v>
+        <v>0.6394514174100401</v>
       </c>
       <c r="E15" t="n">
         <v>-6.6547</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6279286500837664</v>
+        <v>0.6279286500837663</v>
       </c>
       <c r="E19" t="n">
         <v>-7.764</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6732030541732316</v>
+        <v>0.6732030541732315</v>
       </c>
       <c r="E3" t="n">
         <v>0.9026</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6457214997488588</v>
+        <v>0.6457214997488587</v>
       </c>
       <c r="E7" t="n">
         <v>-1.6947</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6437958460259671</v>
+        <v>0.643795846025967</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8333</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6381690166530873</v>
+        <v>0.6381690166530872</v>
       </c>
       <c r="E13" t="n">
         <v>10.571</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6360770549312599</v>
+        <v>0.6360770549312598</v>
       </c>
       <c r="E16" t="n">
         <v>0.625</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6319940867141863</v>
+        <v>0.6319940867141862</v>
       </c>
       <c r="E18" t="n">
         <v>-13.9333</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6242786318911263</v>
+        <v>0.6242786318911265</v>
       </c>
       <c r="E20" t="n">
         <v>1.2022</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6535623362516694</v>
+        <v>0.6535623362516693</v>
       </c>
       <c r="E2" t="n">
         <v>3.3318</v>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6484448327097735</v>
+        <v>0.6484448327097738</v>
       </c>
       <c r="E7" t="n">
         <v>4.4589</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6469194589572084</v>
+        <v>0.6469194589572085</v>
       </c>
       <c r="E10" t="n">
         <v>4.6038</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6440561702339898</v>
+        <v>0.6440561702339899</v>
       </c>
       <c r="E11" t="n">
         <v>3.278</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6381086003854956</v>
+        <v>0.6381086003854954</v>
       </c>
       <c r="E15" t="n">
         <v>-3.125</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6332616296361868</v>
+        <v>0.6332616296361867</v>
       </c>
       <c r="E17" t="n">
         <v>0.372</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6305530536596109</v>
+        <v>0.6305530536596108</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4854</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6375393073270098</v>
+        <v>0.6375393073270097</v>
       </c>
       <c r="E10" t="n">
         <v>0.3968</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6351398837663508</v>
+        <v>0.6351398837663507</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8038</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6270957246001907</v>
+        <v>0.6270957246001906</v>
       </c>
       <c r="E14" t="n">
         <v>-3.5788</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6270349309965159</v>
+        <v>0.627034930996516</v>
       </c>
       <c r="E15" t="n">
         <v>1.7999</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6239144071664555</v>
+        <v>0.6239144071664557</v>
       </c>
       <c r="E16" t="n">
         <v>3.4401</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6230519539983551</v>
+        <v>0.623051953998355</v>
       </c>
       <c r="E17" t="n">
         <v>5.2152</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6228141128826765</v>
+        <v>0.6228141128826766</v>
       </c>
       <c r="E18" t="n">
         <v>-3.2264</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6222082175082193</v>
+        <v>0.6222082175082194</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2684</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6564984073150286</v>
+        <v>0.656498407315029</v>
       </c>
       <c r="E6" t="n">
         <v>11.6497</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6478478352315363</v>
+        <v>0.6478478352315364</v>
       </c>
       <c r="E10" t="n">
         <v>4.5947</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6422698529543589</v>
+        <v>0.6422698529543591</v>
       </c>
       <c r="E13" t="n">
         <v>8.254899999999999</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6341442974911928</v>
+        <v>0.6341442974911927</v>
       </c>
       <c r="E16" t="n">
         <v>1.3859</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6337538117262443</v>
+        <v>0.6337538117262445</v>
       </c>
       <c r="E17" t="n">
         <v>5.7026</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6300020886416372</v>
+        <v>0.6300020886416371</v>
       </c>
       <c r="E20" t="n">
         <v>8.5999</v>

--- a/results/reports/year_2024_report.xlsx
+++ b/results/reports/year_2024_report.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6556039608270122</v>
+        <v>0.6556039608270123</v>
       </c>
       <c r="E5" t="n">
         <v>0.8264</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6386840881987571</v>
+        <v>0.638684088198757</v>
       </c>
       <c r="E10" t="n">
         <v>1.8858</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.632625159178728</v>
+        <v>0.6326251591787279</v>
       </c>
       <c r="E12" t="n">
         <v>-3.4037</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6301691899416975</v>
+        <v>0.6301691899416976</v>
       </c>
       <c r="E13" t="n">
         <v>0.4109</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6291175453069012</v>
+        <v>0.629117545306901</v>
       </c>
       <c r="E14" t="n">
         <v>-1.2925</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6243024707943738</v>
+        <v>0.6243024707943736</v>
       </c>
       <c r="E17" t="n">
         <v>2.6484</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6942679918661072</v>
+        <v>0.6942679918661071</v>
       </c>
       <c r="E2" t="n">
         <v>6.7517</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6694470348391421</v>
+        <v>0.6694470348391419</v>
       </c>
       <c r="E3" t="n">
         <v>-2.7625</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6305303928133676</v>
+        <v>0.6305303928133678</v>
       </c>
       <c r="E10" t="n">
         <v>-0.5351</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6303270086513433</v>
+        <v>0.6303270086513434</v>
       </c>
       <c r="E11" t="n">
         <v>2.8747</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6264892644085198</v>
+        <v>0.62648926440852</v>
       </c>
       <c r="E13" t="n">
         <v>1.1667</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6193358052792194</v>
+        <v>0.6193358052792195</v>
       </c>
       <c r="E17" t="n">
         <v>2.1436</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6157714447560619</v>
+        <v>0.6157714447560618</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2569</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6133464344468577</v>
+        <v>0.6133464344468578</v>
       </c>
       <c r="E20" t="n">
         <v>3.2636</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6083093973797047</v>
+        <v>0.6083093973797046</v>
       </c>
       <c r="E21" t="n">
         <v>3.8251</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6899846102587928</v>
+        <v>0.689984610258793</v>
       </c>
       <c r="E2" t="n">
         <v>-2.4228</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6874043324915097</v>
+        <v>0.6874043324915096</v>
       </c>
       <c r="E3" t="n">
         <v>-13.9116</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6756533694046594</v>
+        <v>0.6756533694046596</v>
       </c>
       <c r="E4" t="n">
         <v>-3.7037</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6661991219847831</v>
+        <v>0.6661991219847834</v>
       </c>
       <c r="E6" t="n">
         <v>7.3221</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6603843315859463</v>
+        <v>0.6603843315859466</v>
       </c>
       <c r="E7" t="n">
         <v>8.3833</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6554928953192254</v>
+        <v>0.6554928953192253</v>
       </c>
       <c r="E10" t="n">
         <v>0.6605</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6524176660637546</v>
+        <v>0.6524176660637545</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5652</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6502124792741607</v>
+        <v>0.6502124792741606</v>
       </c>
       <c r="E14" t="n">
         <v>0.3047</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6477409153575399</v>
+        <v>0.6477409153575396</v>
       </c>
       <c r="E16" t="n">
         <v>-0.8211000000000001</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6369849098667296</v>
+        <v>0.6369849098667298</v>
       </c>
       <c r="E21" t="n">
         <v>2.3765</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6736999274289489</v>
+        <v>0.6736999274289488</v>
       </c>
       <c r="E4" t="n">
         <v>1.025</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6727657373198936</v>
+        <v>0.6727657373198934</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2786</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6700355674664951</v>
+        <v>0.670035567466495</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6652</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6517765558320354</v>
+        <v>0.6517765558320356</v>
       </c>
       <c r="E10" t="n">
         <v>-2.3355</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6418525746447508</v>
+        <v>0.6418525746447509</v>
       </c>
       <c r="E13" t="n">
         <v>-1.0482</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6300433882563484</v>
+        <v>0.6300433882563483</v>
       </c>
       <c r="E18" t="n">
         <v>0.4808</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6288495626342244</v>
+        <v>0.6288495626342243</v>
       </c>
       <c r="E19" t="n">
         <v>-3.168</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6978824958340608</v>
+        <v>0.6978824958340607</v>
       </c>
       <c r="E2" t="n">
         <v>-2.1488</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6776627700020331</v>
+        <v>0.677662770002033</v>
       </c>
       <c r="E6" t="n">
         <v>10.8214</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6635289018462965</v>
+        <v>0.6635289018462968</v>
       </c>
       <c r="E15" t="n">
         <v>0.0626</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6619570252890483</v>
+        <v>0.6619570252890482</v>
       </c>
       <c r="E16" t="n">
         <v>2.8026</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6566963221428417</v>
+        <v>0.6566963221428418</v>
       </c>
       <c r="E19" t="n">
         <v>-1.7486</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7274771975114342</v>
+        <v>0.727477197511434</v>
       </c>
       <c r="E3" t="n">
         <v>2.8002</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6926411430159818</v>
+        <v>0.692641143015982</v>
       </c>
       <c r="E4" t="n">
         <v>8.4793</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.690664106015341</v>
+        <v>0.6906641060153409</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1364</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6864711013497826</v>
+        <v>0.6864711013497827</v>
       </c>
       <c r="E6" t="n">
         <v>12.4972</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6712685480544046</v>
+        <v>0.6712685480544045</v>
       </c>
       <c r="E9" t="n">
         <v>6.4966</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6698461574753177</v>
+        <v>0.6698461574753176</v>
       </c>
       <c r="E10" t="n">
         <v>6.6743</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6684340203428593</v>
+        <v>0.6684340203428591</v>
       </c>
       <c r="E12" t="n">
         <v>4.2262</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6567025849273825</v>
+        <v>0.6567025849273826</v>
       </c>
       <c r="E16" t="n">
         <v>0.4222</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6439159046561547</v>
+        <v>0.6439159046561548</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6855</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7206311037398363</v>
+        <v>0.7206311037398362</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7252</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6779855098628232</v>
+        <v>0.6779855098628234</v>
       </c>
       <c r="E4" t="n">
         <v>0.9258999999999999</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6724670800507139</v>
+        <v>0.672467080050714</v>
       </c>
       <c r="E5" t="n">
         <v>-1.0617</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6586451339925223</v>
+        <v>0.6586451339925222</v>
       </c>
       <c r="E7" t="n">
         <v>10.5879</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6551382816736218</v>
+        <v>0.6551382816736219</v>
       </c>
       <c r="E8" t="n">
         <v>-11.3255</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6545568736746457</v>
+        <v>0.6545568736746454</v>
       </c>
       <c r="E11" t="n">
         <v>-1.5427</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6478870863647488</v>
+        <v>0.6478870863647489</v>
       </c>
       <c r="E13" t="n">
         <v>0.5041</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6293237475647263</v>
+        <v>0.6293237475647262</v>
       </c>
       <c r="E19" t="n">
         <v>16.1728</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6948490177002188</v>
+        <v>0.6948490177002189</v>
       </c>
       <c r="E2" t="n">
         <v>3.0658</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6732030541732315</v>
+        <v>0.6732030541732316</v>
       </c>
       <c r="E3" t="n">
         <v>0.9026</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6668209222370836</v>
+        <v>0.6668209222370837</v>
       </c>
       <c r="E4" t="n">
         <v>-2.5341</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6458246469615215</v>
+        <v>0.6458246469615214</v>
       </c>
       <c r="E6" t="n">
         <v>5.7466</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6457214997488587</v>
+        <v>0.6457214997488588</v>
       </c>
       <c r="E7" t="n">
         <v>-1.6947</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6432209526069953</v>
+        <v>0.6432209526069954</v>
       </c>
       <c r="E9" t="n">
         <v>5.0911</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6428621419986308</v>
+        <v>0.642862141998631</v>
       </c>
       <c r="E10" t="n">
         <v>0.6418</v>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6399133255527133</v>
+        <v>0.6399133255527132</v>
       </c>
       <c r="E12" t="n">
         <v>7.9418</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6381690166530872</v>
+        <v>0.6381690166530873</v>
       </c>
       <c r="E13" t="n">
         <v>10.571</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6362436471346519</v>
+        <v>0.6362436471346518</v>
       </c>
       <c r="E15" t="n">
         <v>-10.1493</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6535623362516693</v>
+        <v>0.6535623362516694</v>
       </c>
       <c r="E2" t="n">
         <v>3.3318</v>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6523070681550629</v>
+        <v>0.6523070681550631</v>
       </c>
       <c r="E4" t="n">
         <v>3.8711</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6496717330284842</v>
+        <v>0.6496717330284844</v>
       </c>
       <c r="E6" t="n">
         <v>2.6538</v>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6484448327097738</v>
+        <v>0.6484448327097736</v>
       </c>
       <c r="E7" t="n">
         <v>4.4589</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6440561702339899</v>
+        <v>0.6440561702339898</v>
       </c>
       <c r="E11" t="n">
         <v>3.278</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6332616296361867</v>
+        <v>0.6332616296361868</v>
       </c>
       <c r="E17" t="n">
         <v>0.372</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6305530536596108</v>
+        <v>0.6305530536596109</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4854</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6303257808403838</v>
+        <v>0.6303257808403837</v>
       </c>
       <c r="E20" t="n">
         <v>3.1819</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6285202509835358</v>
+        <v>0.6285202509835359</v>
       </c>
       <c r="E21" t="n">
         <v>3.4068</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6944775553229195</v>
+        <v>0.6944775553229197</v>
       </c>
       <c r="E2" t="n">
         <v>-2.4594</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6784074096967707</v>
+        <v>0.6784074096967704</v>
       </c>
       <c r="E3" t="n">
         <v>-9.2309</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6696153899135955</v>
+        <v>0.6696153899135954</v>
       </c>
       <c r="E4" t="n">
         <v>9.302300000000001</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6375393073270097</v>
+        <v>0.6375393073270098</v>
       </c>
       <c r="E10" t="n">
         <v>0.3968</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6351398837663507</v>
+        <v>0.6351398837663508</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8038</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6270957246001906</v>
+        <v>0.6270957246001907</v>
       </c>
       <c r="E14" t="n">
         <v>-3.5788</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.627034930996516</v>
+        <v>0.6270349309965159</v>
       </c>
       <c r="E15" t="n">
         <v>1.7999</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6228141128826766</v>
+        <v>0.6228141128826767</v>
       </c>
       <c r="E18" t="n">
         <v>-3.2264</v>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6856473379269338</v>
+        <v>0.6856473379269339</v>
       </c>
       <c r="E2" t="n">
         <v>2.1575</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6638481763577682</v>
+        <v>0.6638481763577683</v>
       </c>
       <c r="E3" t="n">
         <v>1.1194</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.66288366769424</v>
+        <v>0.6628836676942401</v>
       </c>
       <c r="E4" t="n">
         <v>-1.9643</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6570531527779633</v>
+        <v>0.6570531527779635</v>
       </c>
       <c r="E5" t="n">
         <v>1.6713</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.656498407315029</v>
+        <v>0.6564984073150287</v>
       </c>
       <c r="E6" t="n">
         <v>11.6497</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6478478352315364</v>
+        <v>0.6478478352315363</v>
       </c>
       <c r="E10" t="n">
         <v>4.5947</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6300020886416371</v>
+        <v>0.6300020886416372</v>
       </c>
       <c r="E20" t="n">
         <v>8.5999</v>
